--- a/characterization/out/out1/out1.xlsx
+++ b/characterization/out/out1/out1.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characterization" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterizationOld" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharacterizationNew" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,7 +728,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Pressure Integral (MPa*s)</t>
+          <t>Full Pressure Integral (MPa*s)</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -855,7 +856,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Average Pressure (MPa)</t>
+          <t>Average Pressure (using full fire) (MPa)</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -919,11 +920,11 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Average Burnrate (mm/s)</t>
+          <t>Average Burnrate (using full fire) (mm/s)</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>4.05402973936427</v>
+        <v>4.041832530086078</v>
       </c>
     </row>
     <row r="8">
@@ -983,11 +984,11 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Impulse (lbf*s)</t>
+          <t>Average Pressure (using points above average) (MPa)</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>287.1698168739581</v>
+        <v>2.763920541652142</v>
       </c>
     </row>
     <row r="9">
@@ -1047,11 +1048,11 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Pressure Integral (psig*s)</t>
+          <t>Average Burnrate (using points above average) (mm/s)</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>993.3487485792778</v>
+        <v>5.111268030844618</v>
       </c>
     </row>
     <row r="10">
@@ -1111,11 +1112,11 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>C* (ft/s)</t>
+          <t>Impulse (lbf*s)</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>4906.967022018958</v>
+        <v>287.1698168739581</v>
       </c>
     </row>
     <row r="11">
@@ -1175,11 +1176,11 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Average Pressure (psig)</t>
+          <t>Full Pressure Integral (psig*s)</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>314.3508698035691</v>
+        <v>993.3487485792778</v>
       </c>
     </row>
     <row r="12">
@@ -1239,11 +1240,11 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Average Burnrate (in/s)</t>
+          <t>C* (ft/s)</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0.1596075562417453</v>
+        <v>4906.967022018958</v>
       </c>
     </row>
     <row r="13">
@@ -1303,11 +1304,11 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ISP (sec)</t>
+          <t>Average Pressure (using full fire) (psig)</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>188.2438775450109</v>
+        <v>314.3508698035691</v>
       </c>
     </row>
     <row r="14">
@@ -1365,8 +1366,14 @@
       <c r="R14" t="n">
         <v>0.1831493679691062</v>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Average Burnrate (in/s) (using full fire)</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1591273508927419</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1423,8 +1430,14 @@
       <c r="R15" t="n">
         <v>0.1861325971301015</v>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Average Pressure (using points above average) (psig)</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>400.8727826267029</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1481,8 +1494,14 @@
       <c r="R16" t="n">
         <v>0.186503166492563</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Average Burnrate (using points above average) (in/s)</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2012311335011557</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1539,8 +1558,14 @@
       <c r="R17" t="n">
         <v>0.1882038398130086</v>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ISP (sec)</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>188.2438775450109</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -5260,7 +5285,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Pressure Integral (MPa*s)</t>
+          <t>Full Pressure Integral (MPa*s)</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -5388,7 +5413,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Average Pressure (MPa)</t>
+          <t>Average Pressure (using full fire) (MPa)</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -5452,11 +5477,11 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Average Burnrate (mm/s)</t>
+          <t>Average Burnrate (using full fire) (mm/s)</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>4.18334586539266</v>
+        <v>4.254978472732983</v>
       </c>
     </row>
     <row r="8">
@@ -5516,11 +5541,11 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Impulse (lbf*s)</t>
+          <t>Average Pressure (using points above average) (MPa)</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>280.2944475423513</v>
+        <v>3.248606501539229</v>
       </c>
     </row>
     <row r="9">
@@ -5580,11 +5605,11 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Pressure Integral (psig*s)</t>
+          <t>Average Burnrate (using points above average) (mm/s)</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>1092.014030435683</v>
+        <v>5.408119403133058</v>
       </c>
     </row>
     <row r="10">
@@ -5644,11 +5669,11 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>C* (ft/s)</t>
+          <t>Impulse (lbf*s)</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>5102.034198575786</v>
+        <v>280.2944475423513</v>
       </c>
     </row>
     <row r="11">
@@ -5708,11 +5733,11 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Average Pressure (psig)</t>
+          <t>Full Pressure Integral (psig*s)</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>363.7621686994284</v>
+        <v>1092.014030435683</v>
       </c>
     </row>
     <row r="12">
@@ -5772,11 +5797,11 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Average Burnrate (in/s)</t>
+          <t>C* (ft/s)</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0.1646987450550956</v>
+        <v>5102.034198575786</v>
       </c>
     </row>
     <row r="13">
@@ -5836,11 +5861,11 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ISP (sec)</t>
+          <t>Average Pressure (using full fire) (psig)</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>183.7369756824667</v>
+        <v>363.7621686994284</v>
       </c>
     </row>
     <row r="14">
@@ -5898,8 +5923,14 @@
       <c r="R14" t="n">
         <v>0.1691730481724457</v>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Average Burnrate (in/s) (using full fire)</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1675189279693448</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -5956,8 +5987,14 @@
       <c r="R15" t="n">
         <v>0.1729375470320409</v>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Average Pressure (using points above average) (psig)</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>471.1705377582196</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -6014,8 +6051,14 @@
       <c r="R16" t="n">
         <v>0.1753736013128037</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Average Burnrate (using points above average) (in/s)</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2129182017132888</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -6072,8 +6115,14 @@
       <c r="R17" t="n">
         <v>0.1785005451706855</v>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ISP (sec)</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>183.7369756824667</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -9561,7 +9610,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Pressure Integral (MPa*s)</t>
+          <t>Full Pressure Integral (MPa*s)</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -9689,7 +9738,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Average Pressure (MPa)</t>
+          <t>Average Pressure (using full fire) (MPa)</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -9753,11 +9802,11 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Average Burnrate (mm/s)</t>
+          <t>Average Burnrate (using full fire) (mm/s)</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>4.30999455351504</v>
+        <v>4.302532935072866</v>
       </c>
     </row>
     <row r="8">
@@ -9817,11 +9866,11 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Impulse (lbf*s)</t>
+          <t>Average Pressure (using points above average) (MPa)</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>289.3762587523703</v>
+        <v>3.546304583953522</v>
       </c>
     </row>
     <row r="9">
@@ -9881,11 +9930,11 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Pressure Integral (psig*s)</t>
+          <t>Average Burnrate (using points above average) (mm/s)</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>1155.231503595463</v>
+        <v>5.581836910624572</v>
       </c>
     </row>
     <row r="10">
@@ -9945,11 +9994,11 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>C* (ft/s)</t>
+          <t>Impulse (lbf*s)</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>5077.028328865798</v>
+        <v>289.3762587523703</v>
       </c>
     </row>
     <row r="11">
@@ -10009,11 +10058,11 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Average Pressure (psig)</t>
+          <t>Full Pressure Integral (psig*s)</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>389.0978456030527</v>
+        <v>1155.231503595463</v>
       </c>
     </row>
     <row r="12">
@@ -10073,11 +10122,11 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Average Burnrate (in/s)</t>
+          <t>C* (ft/s)</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0.1696849165713425</v>
+        <v>5077.028328865798</v>
       </c>
     </row>
     <row r="13">
@@ -10137,11 +10186,11 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ISP (sec)</t>
+          <t>Average Pressure (using full fire) (psig)</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>189.6902314107875</v>
+        <v>389.0978456030527</v>
       </c>
     </row>
     <row r="14">
@@ -10199,8 +10248,14 @@
       <c r="R14" t="n">
         <v>0.1574542322366897</v>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Average Burnrate (in/s) (using full fire)</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1693911519071123</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -10257,8 +10312,14 @@
       <c r="R15" t="n">
         <v>0.1612236363779067</v>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Average Pressure (using points above average) (psig)</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>514.3479941581477</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -10315,8 +10376,14 @@
       <c r="R16" t="n">
         <v>0.1642047448147796</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Average Burnrate (using points above average) (in/s)</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2197574773549804</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -10373,8 +10440,14 @@
       <c r="R17" t="n">
         <v>0.1679482796174904</v>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ISP (sec)</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>189.6902314107875</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -13519,7 +13592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13555,7 +13628,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.264517615750071</v>
+        <v>3.208067467435161</v>
       </c>
     </row>
     <row r="4">
@@ -13568,7 +13641,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2770474995445706</v>
+        <v>0.3011424723224058</v>
       </c>
     </row>
     <row r="5">
@@ -13592,7 +13665,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03237073898836026</v>
+        <v>0.0282160557422733</v>
       </c>
     </row>
     <row r="7">
@@ -13605,7 +13678,155 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2770475031812422</v>
+        <v>0.3011424601959523</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R^2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9778325083573611</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Metric (MPa and mm):</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.569521401001583</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3529753624705195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Imperial (psig and in):</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02425643444460022</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3529753624981126</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R^2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.999931783880587</v>
       </c>
     </row>
   </sheetData>
